--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -397,306 +397,235 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:I18"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
+      <c r="A1" t="str">
+        <v>Dia</v>
+      </c>
       <c r="B1" t="str">
-        <v>Dia</v>
+        <v>Hora</v>
       </c>
       <c r="C1" t="str">
-        <v>Hora</v>
+        <v>Punto de encuentro</v>
       </c>
       <c r="D1" t="str">
-        <v>Punto de encuentro</v>
+        <v>Territorio</v>
       </c>
       <c r="E1" t="str">
-        <v>Territorio</v>
+        <v>Conductor</v>
       </c>
       <c r="F1" t="str">
-        <v>Conductor</v>
-      </c>
-      <c r="G1" t="str">
         <v>Grupos</v>
       </c>
-      <c r="I1" t="str">
+      <c r="H1" t="str">
         <v xml:space="preserve">      </v>
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="str">
+        <v>Lunes</v>
+      </c>
       <c r="B2" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Casa Florencia C</v>
+      </c>
+      <c r="D2" t="str">
+        <v>11</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Oscar M.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
         <v>Lunes</v>
       </c>
-      <c r="C2" t="str">
+      <c r="B3" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Calle 1149 Y 1122</v>
+      </c>
+      <c r="D3" t="str">
+        <v>4</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Joaquin B.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Martes</v>
+      </c>
+      <c r="B4" t="str">
         <v>10:00</v>
       </c>
-      <c r="D2" t="str">
-        <v>Calle 1149 Y 1120</v>
-      </c>
-      <c r="E2" t="str">
-        <v>3</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Oscar M.</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="str">
-        <v>Lunes</v>
-      </c>
-      <c r="C3" t="str">
+      <c r="C4" t="str">
+        <v>Calle 1149 Y 1146</v>
+      </c>
+      <c r="D4" t="str">
+        <v>23</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Horacio F.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Martes</v>
+      </c>
+      <c r="B5" t="str">
         <v>16:00</v>
       </c>
-      <c r="D3" t="str">
-        <v>Calle 1209 Y 1272</v>
-      </c>
-      <c r="E3" t="str">
-        <v>31</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Joaquin B.</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="str">
-        <v>Martes</v>
-      </c>
-      <c r="C4" t="str">
+      <c r="C5" t="str">
+        <v>Calle 1149 Y 1130</v>
+      </c>
+      <c r="D5" t="str">
+        <v>12</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Tobias B.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Miercoles</v>
+      </c>
+      <c r="B6" t="str">
         <v>10:00</v>
       </c>
-      <c r="D4" t="str">
-        <v>Calle 1149 Y 1146</v>
-      </c>
-      <c r="E4" t="str">
-        <v>23</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Horacio F.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="str">
-        <v>Martes</v>
-      </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
+        <v>Calle 1149 Y 1122</v>
+      </c>
+      <c r="D6" t="str">
+        <v>5</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Rodolfo P.</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Miercoles</v>
+      </c>
+      <c r="B7" t="str">
         <v>16:00</v>
       </c>
-      <c r="D5" t="str">
-        <v>Calle 1149 Y 1130</v>
-      </c>
-      <c r="E5" t="str">
-        <v>12</v>
-      </c>
-      <c r="F5" t="str">
+      <c r="C7" t="str">
+        <v>Calle 1209 Y 1268</v>
+      </c>
+      <c r="D7" t="str">
+        <v>63</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Benjamin S.</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Jueves</v>
+      </c>
+      <c r="B8" t="str">
+        <v>10:00</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Calle 1149 Y 1134</v>
+      </c>
+      <c r="D8" t="str">
+        <v>15</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Dylan F.</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Jueves</v>
+      </c>
+      <c r="B9" t="str">
+        <v>16:00</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Calle 1209 Y 1260</v>
+      </c>
+      <c r="D9" t="str">
+        <v>64</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Daniel C.</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Jueves</v>
+      </c>
+      <c r="B10" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Predicacion Telefonica Zoom</v>
+      </c>
+      <c r="E10" t="str">
         <v>Tobias B.</v>
       </c>
-      <c r="G5" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="str">
-        <v>Miercoles</v>
-      </c>
-      <c r="C6" t="str">
-        <v>10:00</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Calle 1149 Y 1122</v>
-      </c>
-      <c r="E6" t="str">
-        <v>5</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Rodolfo P.</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="str">
-        <v>Miercoles</v>
-      </c>
-      <c r="C7" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Calle 1209 Y 1268</v>
-      </c>
-      <c r="E7" t="str">
-        <v>63</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Benjamin S.</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="str">
-        <v>Jueves</v>
-      </c>
-      <c r="C8" t="str">
-        <v>10:00</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Calle 1149 Y 1134</v>
-      </c>
-      <c r="E8" t="str">
-        <v>15</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Dylan F.</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="str">
-        <v>Jueves</v>
-      </c>
-      <c r="C9" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Calle 1282 Y 1209</v>
-      </c>
-      <c r="E9" t="str">
-        <v>67</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Daniel C.</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="str">
-        <v>Jueves</v>
-      </c>
-      <c r="C10" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Predicacion Telefonica Zoom</v>
-      </c>
       <c r="F10" t="str">
-        <v>Tobias B.</v>
-      </c>
-      <c r="G10" t="str">
         <v>Cong</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="str">
+      <c r="A11" t="str">
         <v>Viernes</v>
       </c>
       <c r="C11" t="str">
-        <v>10:00</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Calle 1149 Y 1142</v>
-      </c>
-      <c r="E11" t="str">
-        <v>21</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Kevin M.</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Cong</v>
+        <v>Asamblea</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="str">
+      <c r="A12" t="str">
         <v>Sabado</v>
       </c>
       <c r="C12" t="str">
-        <v>10:00</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Calle 616 Y 508</v>
-      </c>
-      <c r="E12" t="str">
-        <v>52</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Jonatan S.</v>
-      </c>
-      <c r="G12" t="str">
-        <v>G1,G5 Y G5</v>
+        <v>Asamblea</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="str">
+      <c r="A13" t="str">
         <v>Sabado</v>
       </c>
       <c r="C13" t="str">
-        <v>10:00</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Calle 616 Y 508</v>
-      </c>
-      <c r="E13" t="str">
-        <v>51</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Kevin M.</v>
-      </c>
-      <c r="G13" t="str">
-        <v>G2 Y G3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="str">
-        <v>Sabado</v>
-      </c>
-      <c r="C14" t="str">
-        <v>16:00</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Calle 1209 Y 1262</v>
-      </c>
-      <c r="E14" t="str">
-        <v>34</v>
-      </c>
-      <c r="F14" t="str">
-        <v>Pablo L.</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Cong</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="str">
-        <v>Sabado</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="str">
-        <v>Sabado</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="D18" t="str">
-        <v>Salidas Con Direcciones a Google Maps</v>
+        <v>Asamblea</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="B1:I18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -427,13 +427,13 @@
         <v>Lunes</v>
       </c>
       <c r="B2" t="str">
-        <v>10:00</v>
+        <v>09:30</v>
       </c>
       <c r="C2" t="str">
-        <v>Casa Florencia C</v>
+        <v>Calle 1149 Y 1126</v>
       </c>
       <c r="D2" t="str">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="str">
         <v>Oscar M.</v>
@@ -447,13 +447,13 @@
         <v>Lunes</v>
       </c>
       <c r="B3" t="str">
-        <v>16:00</v>
+        <v>16:30</v>
       </c>
       <c r="C3" t="str">
-        <v>Calle 1149 Y 1122</v>
+        <v>Calle 1149 Y 1126</v>
       </c>
       <c r="D3" t="str">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3" t="str">
         <v>Joaquin B.</v>
@@ -467,13 +467,13 @@
         <v>Martes</v>
       </c>
       <c r="B4" t="str">
-        <v>10:00</v>
+        <v>09:30</v>
       </c>
       <c r="C4" t="str">
-        <v>Calle 1149 Y 1146</v>
+        <v>Calle 1282 Y 1215</v>
       </c>
       <c r="D4" t="str">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="E4" t="str">
         <v>Horacio F.</v>
@@ -487,13 +487,13 @@
         <v>Martes</v>
       </c>
       <c r="B5" t="str">
-        <v>16:00</v>
+        <v>16:30</v>
       </c>
       <c r="C5" t="str">
-        <v>Calle 1149 Y 1130</v>
+        <v>Calle 1149 Y 1126</v>
       </c>
       <c r="D5" t="str">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E5" t="str">
         <v>Tobias B.</v>
@@ -507,13 +507,13 @@
         <v>Miercoles</v>
       </c>
       <c r="B6" t="str">
-        <v>10:00</v>
+        <v>09:30</v>
       </c>
       <c r="C6" t="str">
-        <v>Calle 1149 Y 1122</v>
+        <v>Calle 1215 Y 1286</v>
       </c>
       <c r="D6" t="str">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E6" t="str">
         <v>Rodolfo P.</v>
@@ -527,13 +527,13 @@
         <v>Miercoles</v>
       </c>
       <c r="B7" t="str">
-        <v>16:00</v>
+        <v>16:30</v>
       </c>
       <c r="C7" t="str">
-        <v>Calle 1209 Y 1268</v>
+        <v>Calle 1211 Y 1244</v>
       </c>
       <c r="D7" t="str">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E7" t="str">
         <v>Benjamin S.</v>
@@ -547,13 +547,13 @@
         <v>Jueves</v>
       </c>
       <c r="B8" t="str">
-        <v>10:00</v>
+        <v>09:30</v>
       </c>
       <c r="C8" t="str">
-        <v>Calle 1149 Y 1134</v>
+        <v>Calle 1149 Y 1120</v>
       </c>
       <c r="D8" t="str">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E8" t="str">
         <v>Dylan F.</v>
@@ -567,10 +567,10 @@
         <v>Jueves</v>
       </c>
       <c r="B9" t="str">
-        <v>16:00</v>
+        <v>16:30</v>
       </c>
       <c r="C9" t="str">
-        <v>Calle 1209 Y 1260</v>
+        <v>Calle 1211 Y 1254</v>
       </c>
       <c r="D9" t="str">
         <v>64</v>
@@ -603,24 +603,45 @@
       <c r="A11" t="str">
         <v>Viernes</v>
       </c>
+      <c r="B11" t="str">
+        <v>09:30</v>
+      </c>
       <c r="C11" t="str">
-        <v>Asamblea</v>
+        <v>Calle 1149 Y 1146</v>
+      </c>
+      <c r="D11" t="str">
+        <v>24</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Kevin M.</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Cong</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
         <v>Sabado</v>
       </c>
+      <c r="B12" t="str">
+        <v>09:45</v>
+      </c>
       <c r="C12" t="str">
-        <v>Asamblea</v>
+        <v>Calle 621 Y 510</v>
+      </c>
+      <c r="D12" t="str">
+        <v>77</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Daniel C.</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Cong</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>Sabado</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Asamblea</v>
       </c>
     </row>
   </sheetData>

--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -450,10 +450,10 @@
         <v>16:30</v>
       </c>
       <c r="C3" t="str">
-        <v>Calle 1149 Y 1126</v>
+        <v>Calle 1209 Y 1270</v>
       </c>
       <c r="D3" t="str">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="E3" t="str">
         <v>Joaquin B.</v>
@@ -470,7 +470,7 @@
         <v>09:30</v>
       </c>
       <c r="C4" t="str">
-        <v>Calle 1282 Y 1215</v>
+        <v>Calle 1282 Y 1217</v>
       </c>
       <c r="D4" t="str">
         <v>60</v>
@@ -510,10 +510,10 @@
         <v>09:30</v>
       </c>
       <c r="C6" t="str">
-        <v>Calle 1215 Y 1286</v>
+        <v>Calle 1149 Y 1146</v>
       </c>
       <c r="D6" t="str">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E6" t="str">
         <v>Rodolfo P.</v>
@@ -530,10 +530,10 @@
         <v>16:30</v>
       </c>
       <c r="C7" t="str">
-        <v>Calle 1211 Y 1244</v>
+        <v>Calle 1282 Y 1201</v>
       </c>
       <c r="D7" t="str">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="E7" t="str">
         <v>Benjamin S.</v>
@@ -550,10 +550,10 @@
         <v>09:30</v>
       </c>
       <c r="C8" t="str">
-        <v>Calle 1149 Y 1120</v>
+        <v>Calle 1155 Y 1142</v>
       </c>
       <c r="D8" t="str">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E8" t="str">
         <v>Dylan F.</v>
@@ -570,10 +570,10 @@
         <v>16:30</v>
       </c>
       <c r="C9" t="str">
-        <v>Calle 1211 Y 1254</v>
+        <v>Calle 1211 Y 1286</v>
       </c>
       <c r="D9" t="str">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="E9" t="str">
         <v>Daniel C.</v>
@@ -607,7 +607,7 @@
         <v>09:30</v>
       </c>
       <c r="C11" t="str">
-        <v>Calle 1149 Y 1146</v>
+        <v>Calle 1149 Y 1150</v>
       </c>
       <c r="D11" t="str">
         <v>24</v>
@@ -627,26 +627,81 @@
         <v>09:45</v>
       </c>
       <c r="C12" t="str">
-        <v>Calle 621 Y 510</v>
+        <v xml:space="preserve">Casa Joel (Visita Del Sup de Servicio) </v>
       </c>
       <c r="D12" t="str">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="E12" t="str">
-        <v>Daniel C.</v>
+        <v>Mauro H.</v>
       </c>
       <c r="F12" t="str">
-        <v>Cong</v>
+        <v>G 2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>Sabado</v>
       </c>
+      <c r="B13" t="str">
+        <v>09:45</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Casa Ester Altamirano</v>
+      </c>
+      <c r="D13" t="str">
+        <v>15</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Daniel C.</v>
+      </c>
+      <c r="F13" t="str">
+        <v>G 3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Sabado</v>
+      </c>
+      <c r="B14" t="str">
+        <v>09:45</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Calle 619 Y Av Ing Allan</v>
+      </c>
+      <c r="D14" t="str">
+        <v>47</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Nestor R.</v>
+      </c>
+      <c r="F14" t="str">
+        <v>G1,G4,G5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Sabado</v>
+      </c>
+      <c r="B15" t="str">
+        <v>16:30</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Calle 1149 Y 1128</v>
+      </c>
+      <c r="D15" t="str">
+        <v>10</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Pablo L.</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Cong</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +430,7 @@
         <v>09:30</v>
       </c>
       <c r="C2" t="str">
-        <v>Calle 1149 Y 1126</v>
+        <v xml:space="preserve">Calle 1145 Y 1128 </v>
       </c>
       <c r="D2" t="str">
         <v>9</v>
@@ -470,10 +470,10 @@
         <v>09:30</v>
       </c>
       <c r="C4" t="str">
-        <v>Calle 1282 Y 1217</v>
+        <v>Casa Flia Frattasi</v>
       </c>
       <c r="D4" t="str">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="E4" t="str">
         <v>Horacio F.</v>
@@ -490,10 +490,10 @@
         <v>16:30</v>
       </c>
       <c r="C5" t="str">
-        <v>Calle 1149 Y 1126</v>
+        <v>Calle 1155 Y 1146</v>
       </c>
       <c r="D5" t="str">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E5" t="str">
         <v>Tobias B.</v>
@@ -510,7 +510,7 @@
         <v>09:30</v>
       </c>
       <c r="C6" t="str">
-        <v>Calle 1149 Y 1146</v>
+        <v>Calle 1149 Y 1142</v>
       </c>
       <c r="D6" t="str">
         <v>23</v>
@@ -530,10 +530,10 @@
         <v>16:30</v>
       </c>
       <c r="C7" t="str">
-        <v>Calle 1282 Y 1201</v>
+        <v>Calle 1209 Y 1282</v>
       </c>
       <c r="D7" t="str">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E7" t="str">
         <v>Benjamin S.</v>
@@ -550,10 +550,10 @@
         <v>09:30</v>
       </c>
       <c r="C8" t="str">
-        <v>Calle 1155 Y 1142</v>
+        <v>Casa De America</v>
       </c>
       <c r="D8" t="str">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="E8" t="str">
         <v>Dylan F.</v>
@@ -570,10 +570,10 @@
         <v>16:30</v>
       </c>
       <c r="C9" t="str">
-        <v>Calle 1211 Y 1286</v>
+        <v>Calle 1149 Y 1126</v>
       </c>
       <c r="D9" t="str">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="E9" t="str">
         <v>Daniel C.</v>
@@ -607,10 +607,10 @@
         <v>09:30</v>
       </c>
       <c r="C11" t="str">
-        <v>Calle 1149 Y 1150</v>
+        <v xml:space="preserve">Casa Flia Sergio Ojeda </v>
       </c>
       <c r="D11" t="str">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E11" t="str">
         <v>Kevin M.</v>
@@ -627,81 +627,21 @@
         <v>09:45</v>
       </c>
       <c r="C12" t="str">
-        <v xml:space="preserve">Casa Joel (Visita Del Sup de Servicio) </v>
+        <v>Casa Flia Daniel Caceres</v>
       </c>
       <c r="D12" t="str">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="E12" t="str">
-        <v>Mauro H.</v>
+        <v>Daniel C.</v>
       </c>
       <c r="F12" t="str">
-        <v>G 2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Sabado</v>
-      </c>
-      <c r="B13" t="str">
-        <v>09:45</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Casa Ester Altamirano</v>
-      </c>
-      <c r="D13" t="str">
-        <v>15</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Daniel C.</v>
-      </c>
-      <c r="F13" t="str">
-        <v>G 3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Sabado</v>
-      </c>
-      <c r="B14" t="str">
-        <v>09:45</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Calle 619 Y Av Ing Allan</v>
-      </c>
-      <c r="D14" t="str">
-        <v>47</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Nestor R.</v>
-      </c>
-      <c r="F14" t="str">
-        <v>G1,G4,G5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Sabado</v>
-      </c>
-      <c r="B15" t="str">
-        <v>16:30</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Calle 1149 Y 1128</v>
-      </c>
-      <c r="D15" t="str">
-        <v>10</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Pablo L.</v>
-      </c>
-      <c r="F15" t="str">
         <v>Cong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -570,10 +570,10 @@
         <v>16:30</v>
       </c>
       <c r="C9" t="str">
-        <v>Calle 1149 Y 1126</v>
+        <v>Calle 1282 Y 1213</v>
       </c>
       <c r="D9" t="str">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="E9" t="str">
         <v>Daniel C.</v>

--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -635,7 +635,7 @@
         <v>Sabado</v>
       </c>
       <c r="B13" t="str">
-        <v>9:30</v>
+        <v>10:30</v>
       </c>
       <c r="C13" t="str">
         <v>Casa De Jose L</v>

--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -658,10 +658,10 @@
         <v>16:30</v>
       </c>
       <c r="C14" t="str">
-        <v>Casa De Oscar M</v>
+        <v>Casa De Rafael M</v>
       </c>
       <c r="D14" t="str">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E14" t="str">
         <v>Javier L.</v>

--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -629,6 +629,9 @@
       <c r="D12" t="str">
         <v>27</v>
       </c>
+      <c r="E12" t="str">
+        <v>Tobias B.</v>
+      </c>
       <c r="F12" t="str">
         <v>Cong</v>
       </c>

--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -626,9 +626,6 @@
       <c r="C12" t="str">
         <v>Predicacion Telefonica Zoom</v>
       </c>
-      <c r="D12" t="str">
-        <v>27</v>
-      </c>
       <c r="E12" t="str">
         <v>Tobias B.</v>
       </c>
@@ -704,7 +701,7 @@
         <v>9:30</v>
       </c>
       <c r="C16" t="str">
-        <v xml:space="preserve">Calle 1155 Y 1150 </v>
+        <v>Calle 616 Y 510</v>
       </c>
       <c r="D16" t="str">
         <v>53</v>
@@ -720,15 +717,25 @@
       <c r="A17" t="str">
         <v>Sabado</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>Salidas Con Direcciones a Google Maps</v>
+      <c r="B17" t="str">
+        <v>16:30</v>
+      </c>
+      <c r="C17" t="str">
+        <v xml:space="preserve">Calle 1155 Y 1150 </v>
+      </c>
+      <c r="D17" t="str">
+        <v>25</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Pablo L.</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Cong</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,7 +433,7 @@
         <v>Calle 1149 Y 1150</v>
       </c>
       <c r="D2" t="str">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="E2" t="str">
         <v>Oscar M.</v>
@@ -498,6 +498,9 @@
       <c r="F5" t="str">
         <v>Cong</v>
       </c>
+      <c r="I5" t="str">
+        <v>s</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -735,7 +738,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,7 +430,7 @@
         <v>9:30</v>
       </c>
       <c r="C2" t="str">
-        <v>Calle 1149 Y 1150</v>
+        <v>Calle 1149 Y 1154</v>
       </c>
       <c r="D2" t="str">
         <v>26</v>
@@ -450,7 +450,7 @@
         <v>16:30</v>
       </c>
       <c r="C3" t="str">
-        <v>Casa De Angela V</v>
+        <v>Casa De Veron Roberto</v>
       </c>
       <c r="D3" t="str">
         <v>29</v>
@@ -487,10 +487,10 @@
         <v>9:45</v>
       </c>
       <c r="C5" t="str">
-        <v>Calle 1209 Y 1272</v>
+        <v>Casa Antunez America</v>
       </c>
       <c r="D5" t="str">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E5" t="str">
         <v>Horacio F.</v>
@@ -499,7 +499,7 @@
         <v>Cong</v>
       </c>
       <c r="I5" t="str">
-        <v>s</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -510,10 +510,10 @@
         <v>16:30</v>
       </c>
       <c r="C6" t="str">
-        <v>Calle 1155 Y 1150</v>
+        <v>Calle 1282 Y 1209</v>
       </c>
       <c r="D6" t="str">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E6" t="str">
         <v>Tobias b.</v>
@@ -547,10 +547,10 @@
         <v>9:30</v>
       </c>
       <c r="C8" t="str">
-        <v>Calle 1215 Y 1286</v>
+        <v xml:space="preserve">Casa Ojeda Sergio </v>
       </c>
       <c r="D8" t="str">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="E8" t="str">
         <v>Rodolfo P.</v>
@@ -567,10 +567,10 @@
         <v>16:30</v>
       </c>
       <c r="C9" t="str">
-        <v>Calle 1209 Y 1268</v>
+        <v>Calle 1155 Y 1138</v>
       </c>
       <c r="D9" t="str">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E9" t="str">
         <v>Benjamin S.</v>
@@ -587,10 +587,10 @@
         <v>9:30</v>
       </c>
       <c r="C10" t="str">
-        <v xml:space="preserve">Calle 1149 Y 1124 </v>
+        <v>Calle 1209 Y 1256</v>
       </c>
       <c r="D10" t="str">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="E10" t="str">
         <v>Dylan F.</v>
@@ -607,10 +607,10 @@
         <v>16:30</v>
       </c>
       <c r="C11" t="str">
-        <v>Calle 1209 Y 1260</v>
+        <v>Calle 1149 Y 1128</v>
       </c>
       <c r="D11" t="str">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E11" t="str">
         <v>Daniel C.</v>
@@ -644,10 +644,10 @@
         <v>9:30</v>
       </c>
       <c r="C13" t="str">
-        <v>Calle 1211 Y 1244</v>
+        <v>Calle 1282 Y 1213</v>
       </c>
       <c r="D13" t="str">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="E13" t="str">
         <v>Kevin M.</v>
@@ -664,81 +664,26 @@
         <v>9:30</v>
       </c>
       <c r="C14" t="str">
-        <v>Calle 616 Y 512</v>
+        <v>Casa Caseres Daniel RURAL</v>
       </c>
       <c r="D14" t="str">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="E14" t="str">
-        <v>Joel S.</v>
+        <v>Daniel C.</v>
       </c>
       <c r="F14" t="str">
-        <v>G2</v>
+        <v>Cong</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>Sabado</v>
       </c>
-      <c r="B15" t="str">
-        <v>9:30</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Calle 616 Y 512</v>
-      </c>
-      <c r="D15" t="str">
-        <v>55</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Joaquin B.</v>
-      </c>
-      <c r="F15" t="str">
-        <v>G1 Y G3</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Sabado</v>
-      </c>
-      <c r="B16" t="str">
-        <v>9:30</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Calle 616 Y 510</v>
-      </c>
-      <c r="D16" t="str">
-        <v>53</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Jonatan S.</v>
-      </c>
-      <c r="F16" t="str">
-        <v>G4 Y G5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Sabado</v>
-      </c>
-      <c r="B17" t="str">
-        <v>16:30</v>
-      </c>
-      <c r="C17" t="str">
-        <v xml:space="preserve">Calle 1155 Y 1150 </v>
-      </c>
-      <c r="D17" t="str">
-        <v>25</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Pablo L.</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Cong</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Salidas 4-8-25.xlsx
+++ b/Salidas 4-8-25.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:H19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,10 +430,10 @@
         <v>9:30</v>
       </c>
       <c r="C2" t="str">
-        <v>Calle 1149 Y 1154</v>
+        <v>Calle 1149 Y 1122</v>
       </c>
       <c r="D2" t="str">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E2" t="str">
         <v>Oscar M.</v>
@@ -450,10 +450,10 @@
         <v>16:30</v>
       </c>
       <c r="C3" t="str">
-        <v>Casa De Veron Roberto</v>
+        <v>Calle 1282 Y 1215</v>
       </c>
       <c r="D3" t="str">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E3" t="str">
         <v>Joaquin B.</v>
@@ -484,22 +484,19 @@
         <v>Martes</v>
       </c>
       <c r="B5" t="str">
-        <v>9:45</v>
+        <v>9:30</v>
       </c>
       <c r="C5" t="str">
-        <v>Casa Antunez America</v>
+        <v>Calle 1149 Y 1124</v>
       </c>
       <c r="D5" t="str">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="str">
         <v>Horacio F.</v>
       </c>
       <c r="F5" t="str">
         <v>Cong</v>
-      </c>
-      <c r="I5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -510,10 +507,10 @@
         <v>16:30</v>
       </c>
       <c r="C6" t="str">
-        <v>Calle 1282 Y 1209</v>
+        <v>Calle 1209 Y 1264</v>
       </c>
       <c r="D6" t="str">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="E6" t="str">
         <v>Tobias b.</v>
@@ -547,10 +544,10 @@
         <v>9:30</v>
       </c>
       <c r="C8" t="str">
-        <v xml:space="preserve">Casa Ojeda Sergio </v>
+        <v>Calle 1149 Y 1132</v>
       </c>
       <c r="D8" t="str">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="E8" t="str">
         <v>Rodolfo P.</v>
@@ -567,10 +564,10 @@
         <v>16:30</v>
       </c>
       <c r="C9" t="str">
-        <v>Calle 1155 Y 1138</v>
+        <v>Calle 1209 Y 1254</v>
       </c>
       <c r="D9" t="str">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="E9" t="str">
         <v>Benjamin S.</v>
@@ -587,10 +584,10 @@
         <v>9:30</v>
       </c>
       <c r="C10" t="str">
-        <v>Calle 1209 Y 1256</v>
+        <v>Calle 1149 Y 1136</v>
       </c>
       <c r="D10" t="str">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E10" t="str">
         <v>Dylan F.</v>
@@ -607,10 +604,10 @@
         <v>16:30</v>
       </c>
       <c r="C11" t="str">
-        <v>Calle 1149 Y 1128</v>
+        <v>Calle 1211 Y 1248</v>
       </c>
       <c r="D11" t="str">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="E11" t="str">
         <v>Daniel C.</v>
@@ -644,10 +641,10 @@
         <v>9:30</v>
       </c>
       <c r="C13" t="str">
-        <v>Calle 1282 Y 1213</v>
+        <v>Calle 1155 Y 1146</v>
       </c>
       <c r="D13" t="str">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E13" t="str">
         <v>Kevin M.</v>
@@ -661,29 +658,69 @@
         <v>Sabado</v>
       </c>
       <c r="B14" t="str">
-        <v>9:30</v>
+        <v xml:space="preserve">  10:00</v>
       </c>
       <c r="C14" t="str">
-        <v>Casa Caseres Daniel RURAL</v>
+        <v>Av Ing Allan Y 611</v>
       </c>
       <c r="D14" t="str">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E14" t="str">
-        <v>Daniel C.</v>
+        <v>Ivan M.</v>
       </c>
       <c r="F14" t="str">
-        <v>Cong</v>
+        <v>G2 Y G5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>Sabado</v>
       </c>
+      <c r="B15" t="str">
+        <v xml:space="preserve">  10:00</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Av Ing Allan Y 614</v>
+      </c>
+      <c r="D15" t="str">
+        <v>46</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Joaquin B.</v>
+      </c>
+      <c r="F15" t="str">
+        <v>G3,G1 Y G4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Sabado</v>
+      </c>
+      <c r="B16" t="str">
+        <v>16:30</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Calle 1209 Y 1260</v>
+      </c>
+      <c r="D16" t="str">
+        <v>64</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Pablo L.</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Cong</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>Salidas Con Direcciones a Google Maps</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
   </ignoredErrors>
 </worksheet>
 </file>